--- a/data/file_generation/input/data_57/美职业开赛时间_2025-10-27_09_30圣地亚哥_VS波特兰伐木者_标盘明细.xlsx
+++ b/data/file_generation/input/data_57/美职业开赛时间_2025-10-27_09_30圣地亚哥_VS波特兰伐木者_标盘明细.xlsx
@@ -21597,26 +21597,18 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
+  <documentManagement/>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D123BFDB-C220-49CC-AC25-57479FFC53C1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03708011-9055-4E66-8E3C-09F79BF09B9A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{661D6B5E-BC7D-4D45-966A-9687ADBCDE3E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0138222-ABAB-4336-8509-EE69C5C614F0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39288501-BCC3-4E9E-9B26-DB599136E9E9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA9F6499-D95D-44E8-82BE-57462A23D388}"/>
 </file>